--- a/data/trans_dic/P22$mutaSS-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,12</t>
+          <t>2,27; 7,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,06</t>
+          <t>0,89; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,76</t>
+          <t>2,26; 6,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,54</t>
+          <t>0,39; 3,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,77</t>
+          <t>0,36; 3,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,35</t>
+          <t>2,41; 5,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,29</t>
+          <t>1,4; 4,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,07</t>
+          <t>0,87; 3,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,43</t>
+          <t>0,44; 2,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,36</t>
+          <t>2,71; 5,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,75</t>
+          <t>2,12; 5,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,21</t>
+          <t>1,6; 5,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,08</t>
+          <t>0,21; 1,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,24</t>
+          <t>2,56; 7,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,21</t>
+          <t>1,37; 4,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,17</t>
+          <t>0,63; 3,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,68</t>
+          <t>0,19; 1,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,7</t>
+          <t>1,5; 3,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,41</t>
+          <t>1,99; 4,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,53</t>
+          <t>1,36; 3,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,45</t>
+          <t>0,31; 1,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,14</t>
+          <t>2,35; 5,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,63</t>
+          <t>1,73; 5,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,71</t>
+          <t>2,41; 7,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,57</t>
+          <t>1,6; 5,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,26</t>
+          <t>0,61; 4,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,15</t>
+          <t>0,57; 3,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,13</t>
+          <t>1,75; 6,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,14</t>
+          <t>0,26; 2,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,57</t>
+          <t>0,62; 4,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,76</t>
+          <t>1,29; 3,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,87</t>
+          <t>2,53; 5,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,42</t>
+          <t>1,13; 3,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,21</t>
+          <t>0,79; 3,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,58</t>
+          <t>2,88; 7,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,51</t>
+          <t>1,01; 4,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,47</t>
+          <t>0,71; 3,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,54</t>
+          <t>0,8; 4,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,55</t>
+          <t>0,76; 3,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,84</t>
+          <t>1,33; 4,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,89</t>
+          <t>0,38; 1,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,94</t>
+          <t>2,1; 4,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,83</t>
+          <t>1,53; 3,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,93</t>
+          <t>0,48; 1,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,4</t>
+          <t>0,66; 2,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 12,99</t>
+          <t>4,97; 13,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,77</t>
+          <t>0,43; 3,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,59</t>
+          <t>1,49; 5,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 12,21</t>
+          <t>4,59; 12,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,19</t>
+          <t>1,31; 4,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,35</t>
+          <t>5,66; 11,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,53</t>
+          <t>0,45; 2,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,34</t>
+          <t>1,69; 4,2</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,92</t>
+          <t>2,56; 7,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,38</t>
+          <t>2,29; 8,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,8</t>
+          <t>3,55; 9,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,83</t>
+          <t>1,78; 6,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,99</t>
+          <t>1,06; 4,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,9</t>
+          <t>0,68; 3,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,94</t>
+          <t>0,68; 4,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,15</t>
+          <t>0,99; 4,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,43</t>
+          <t>2,27; 5,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,3</t>
+          <t>1,68; 5,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,11</t>
+          <t>2,49; 6,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,54</t>
+          <t>1,75; 4,97</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,15</t>
+          <t>1,04; 3,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,91</t>
+          <t>1,94; 4,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,6</t>
+          <t>0,99; 3,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,67</t>
+          <t>1,28; 4,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,04</t>
+          <t>1,33; 3,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,03</t>
+          <t>1,17; 3,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,93</t>
+          <t>0,87; 2,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,54</t>
+          <t>0,26; 1,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,02</t>
+          <t>1,43; 3,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,71</t>
+          <t>1,89; 3,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,73</t>
+          <t>1,21; 2,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,5</t>
+          <t>0,8; 2,48</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,12</t>
+          <t>1,63; 4,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,19</t>
+          <t>0,66; 2,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,87</t>
+          <t>2,21; 4,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,33</t>
+          <t>0,58; 2,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,1</t>
+          <t>4,63; 8,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,29</t>
+          <t>1,12; 3,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,24</t>
+          <t>1,04; 3,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,5</t>
+          <t>1,0; 2,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,61</t>
+          <t>3,57; 5,64</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,48</t>
+          <t>1,03; 2,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,64</t>
+          <t>1,8; 3,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,18</t>
+          <t>0,86; 2,13</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,3</t>
+          <t>2,98; 4,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,28</t>
+          <t>2,13; 3,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,85</t>
+          <t>1,75; 2,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,36</t>
+          <t>1,96; 3,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,04</t>
+          <t>2,75; 4,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,63</t>
+          <t>1,59; 2,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,75</t>
+          <t>0,97; 1,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,11</t>
+          <t>1,31; 2,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,99</t>
+          <t>3,03; 3,96</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,79</t>
+          <t>2,0; 2,77</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,14</t>
+          <t>1,47; 2,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,54</t>
+          <t>1,78; 2,53</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6181; 19369</t>
+          <t>6183; 19486</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2584; 11978</t>
+          <t>2615; 11343</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6705</t>
+          <t>0; 5889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7210; 21044</t>
+          <t>7040; 20993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7535</t>
+          <t>0; 7347</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1252; 10177</t>
+          <t>1131; 9887</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1046; 10847</t>
+          <t>1032; 11246</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6799; 15504</t>
+          <t>6989; 16102</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8018; 22887</t>
+          <t>7449; 21619</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5255; 17870</t>
+          <t>5045; 17658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2592; 14156</t>
+          <t>2536; 13435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15953; 32203</t>
+          <t>16314; 31984</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9868; 28359</t>
+          <t>10440; 28395</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7786; 26281</t>
+          <t>8077; 27127</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1039; 10446</t>
+          <t>1069; 9499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12991; 37517</t>
+          <t>13258; 40031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6684; 21216</t>
+          <t>6898; 20728</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3255; 16604</t>
+          <t>3292; 16400</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>982; 8777</t>
+          <t>986; 9645</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7665; 19076</t>
+          <t>7722; 19512</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20462; 43979</t>
+          <t>19864; 42887</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14025; 36260</t>
+          <t>14022; 35615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3153; 14901</t>
+          <t>3206; 13914</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25576; 53136</t>
+          <t>24317; 52723</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4769; 17936</t>
+          <t>5513; 17997</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8557; 24978</t>
+          <t>7797; 23616</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4755; 17653</t>
+          <t>5079; 17172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1980; 13469</t>
+          <t>1933; 13764</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1867; 10574</t>
+          <t>1927; 11657</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6105; 20921</t>
+          <t>5971; 21633</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>864; 7199</t>
+          <t>859; 7215</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1790; 15939</t>
+          <t>2154; 16990</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8640; 24629</t>
+          <t>8438; 24226</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17463; 39057</t>
+          <t>16803; 37581</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7463; 22329</t>
+          <t>7398; 21544</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5441; 21324</t>
+          <t>5263; 21701</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9948; 27015</t>
+          <t>10281; 27129</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3032; 16853</t>
+          <t>3789; 16975</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2358; 12822</t>
+          <t>2619; 12054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2565; 14183</t>
+          <t>2493; 14257</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2721; 13155</t>
+          <t>2814; 13939</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5976; 18834</t>
+          <t>5157; 18580</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7171</t>
+          <t>0; 6378</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1858; 8977</t>
+          <t>1816; 8901</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15607; 35906</t>
+          <t>15258; 34724</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11198; 29211</t>
+          <t>11655; 29693</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2998; 14626</t>
+          <t>3606; 14019</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5627; 18903</t>
+          <t>5241; 19162</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10365; 26401</t>
+          <t>10096; 27152</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>913; 8014</t>
+          <t>920; 7929</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4723</t>
+          <t>0; 5705</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2609; 9993</t>
+          <t>2658; 10043</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9949; 25352</t>
+          <t>9539; 25371</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6569</t>
+          <t>0; 6855</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4712</t>
+          <t>0; 5380</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2788; 8734</t>
+          <t>2741; 8930</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22728; 46654</t>
+          <t>23277; 46463</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1904; 10916</t>
+          <t>1932; 10972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7298</t>
+          <t>0; 6601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6824; 16830</t>
+          <t>6556; 16262</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6945; 21459</t>
+          <t>6924; 21083</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6564; 22949</t>
+          <t>6278; 22138</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8845; 25788</t>
+          <t>9339; 25813</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5365; 18415</t>
+          <t>4803; 18400</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3000; 13881</t>
+          <t>2940; 12986</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1991; 10923</t>
+          <t>1915; 10982</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1863; 10758</t>
+          <t>1846; 11202</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2620; 10658</t>
+          <t>2541; 10964</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11650; 29823</t>
+          <t>12442; 29827</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10120; 29376</t>
+          <t>9284; 29385</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12512; 32771</t>
+          <t>13342; 32398</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9178; 23887</t>
+          <t>9207; 26181</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5666; 19325</t>
+          <t>6391; 18897</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13001; 32535</t>
+          <t>12878; 32217</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7394; 23517</t>
+          <t>6483; 23605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7385; 29159</t>
+          <t>7995; 27630</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8911; 25719</t>
+          <t>8484; 24900</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8742; 27954</t>
+          <t>8150; 27048</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6207; 20102</t>
+          <t>5939; 19652</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2663; 13073</t>
+          <t>2217; 12714</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17445; 37790</t>
+          <t>17855; 38404</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24750; 50318</t>
+          <t>25676; 51852</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16642; 36524</t>
+          <t>16159; 36422</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12413; 36873</t>
+          <t>11830; 36541</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12123; 30520</t>
+          <t>12049; 30468</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5042; 17050</t>
+          <t>5124; 18264</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16172; 37882</t>
+          <t>17207; 37361</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4060; 21608</t>
+          <t>5359; 22049</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>35589; 63454</t>
+          <t>36309; 64121</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9284; 27090</t>
+          <t>9217; 27512</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8705; 26789</t>
+          <t>8583; 26839</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7058; 17866</t>
+          <t>7189; 18996</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54418; 85526</t>
+          <t>54449; 86048</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17580; 39730</t>
+          <t>16475; 37831</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28820; 58341</t>
+          <t>28806; 55724</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13881; 35801</t>
+          <t>14120; 35067</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>97240; 140671</t>
+          <t>97585; 139614</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>73191; 112473</t>
+          <t>72908; 111940</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60680; 96571</t>
+          <t>59381; 95608</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70274; 116316</t>
+          <t>67672; 116004</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>94062; 136296</t>
+          <t>92763; 135492</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56292; 93592</t>
+          <t>56535; 91782</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33448; 61918</t>
+          <t>34357; 63040</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>48184; 77324</t>
+          <t>47796; 77505</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>200172; 265303</t>
+          <t>201647; 263294</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>139526; 194698</t>
+          <t>139820; 193417</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103529; 148426</t>
+          <t>101890; 146255</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>126393; 180810</t>
+          <t>126820; 180417</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutaSS-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,16</t>
+          <t>2,17; 6,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,85</t>
+          <t>0,88; 4,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,74</t>
+          <t>2,12; 6,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,44</t>
+          <t>0,39; 3,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,91</t>
+          <t>0,54; 4,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,56</t>
+          <t>2,06; 4,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,06</t>
+          <t>1,53; 4,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,03</t>
+          <t>0,96; 3,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,31</t>
+          <t>0,45; 2,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,32</t>
+          <t>2,46; 5,03</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,76</t>
+          <t>2,14; 5,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,38</t>
+          <t>1,68; 5,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,89</t>
+          <t>0,2; 2,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,72</t>
+          <t>2,68; 7,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,11</t>
+          <t>1,38; 4,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,13</t>
+          <t>0,58; 3,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,84</t>
+          <t>0,19; 1,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,79</t>
+          <t>1,52; 3,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,3</t>
+          <t>2,08; 4,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,46</t>
+          <t>1,42; 3,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,36</t>
+          <t>0,31; 1,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,1</t>
+          <t>2,23; 4,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,64</t>
+          <t>1,49; 5,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,29</t>
+          <t>2,63; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,42</t>
+          <t>1,5; 5,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,35</t>
+          <t>0,59; 4,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,48</t>
+          <t>0,56; 3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,34</t>
+          <t>1,81; 6,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,15</t>
+          <t>0,25; 2,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,87</t>
+          <t>0,35; 1,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,7</t>
+          <t>1,32; 3,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,65</t>
+          <t>2,58; 5,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,3</t>
+          <t>1,07; 3,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,26</t>
+          <t>0,67; 2,37</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,61</t>
+          <t>2,97; 7,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,54</t>
+          <t>0,83; 4,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,26</t>
+          <t>0,55; 3,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,56</t>
+          <t>0,59; 3,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,76</t>
+          <t>0,75; 3,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,78</t>
+          <t>1,5; 4,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,87</t>
+          <t>0,59; 2,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,78</t>
+          <t>2,08; 4,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,89</t>
+          <t>1,43; 3,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,85</t>
+          <t>0,42; 2,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,43</t>
+          <t>0,8; 2,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 13,35</t>
+          <t>4,65; 13,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,73</t>
+          <t>0,43; 3,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,62</t>
+          <t>1,47; 5,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 12,22</t>
+          <t>4,71; 12,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,28</t>
+          <t>1,29; 4,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 11,31</t>
+          <t>5,42; 11,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,54</t>
+          <t>0,44; 2,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,2</t>
+          <t>1,71; 4,01</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,78</t>
+          <t>2,59; 7,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,08</t>
+          <t>2,32; 8,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,81</t>
+          <t>3,28; 9,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,82</t>
+          <t>1,69; 6,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,67</t>
+          <t>1,08; 4,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,92</t>
+          <t>0,7; 4,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,1</t>
+          <t>0,71; 4,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,27</t>
+          <t>0,8; 4,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,43</t>
+          <t>2,24; 5,38</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,3</t>
+          <t>1,83; 5,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,04</t>
+          <t>2,44; 6,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,97</t>
+          <t>1,63; 4,15</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,08</t>
+          <t>1,02; 3,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,86</t>
+          <t>1,93; 5,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,61</t>
+          <t>1,0; 3,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,43</t>
+          <t>1,21; 3,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,91</t>
+          <t>1,46; 3,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,9</t>
+          <t>1,21; 3,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,86</t>
+          <t>0,92; 2,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,5</t>
+          <t>0,54; 1,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,07</t>
+          <t>1,41; 3,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,82</t>
+          <t>1,87; 3,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,72</t>
+          <t>1,26; 2,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,48</t>
+          <t>0,99; 2,46</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,11</t>
+          <t>1,66; 4,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,34</t>
+          <t>0,64; 2,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,8</t>
+          <t>2,07; 4,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,37</t>
+          <t>1,09; 2,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,18</t>
+          <t>4,57; 8,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,34</t>
+          <t>1,1; 3,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,25</t>
+          <t>1,07; 3,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,66</t>
+          <t>0,97; 2,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,64</t>
+          <t>3,53; 5,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,36</t>
+          <t>1,06; 2,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,47</t>
+          <t>1,83; 3,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,13</t>
+          <t>1,21; 2,39</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,27</t>
+          <t>2,95; 4,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,27</t>
+          <t>2,07; 3,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,82</t>
+          <t>1,82; 2,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,35</t>
+          <t>2,08; 3,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,01</t>
+          <t>2,74; 3,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,58</t>
+          <t>1,61; 2,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,78</t>
+          <t>0,93; 1,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,12</t>
+          <t>1,42; 2,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,96</t>
+          <t>2,98; 3,93</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,77</t>
+          <t>2,02; 2,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,11</t>
+          <t>1,49; 2,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,53</t>
+          <t>1,86; 2,51</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>22152</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6183; 19486</t>
+          <t>5917; 18402</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2615; 11343</t>
+          <t>2583; 12171</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5889</t>
+          <t>0; 6240</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7040; 20993</t>
+          <t>6746; 19208</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7347</t>
+          <t>0; 7664</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1131; 9887</t>
+          <t>1131; 11163</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1032; 11246</t>
+          <t>1557; 11585</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6989; 16102</t>
+          <t>6503; 14987</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7449; 21619</t>
+          <t>8144; 22424</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5045; 17658</t>
+          <t>5593; 18660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2536; 13435</t>
+          <t>2600; 13504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16314; 31984</t>
+          <t>15597; 31947</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23337</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35870</t>
+          <t>37055</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10440; 28395</t>
+          <t>10575; 29060</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8077; 27127</t>
+          <t>8468; 28105</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1069; 9499</t>
+          <t>1028; 10330</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13258; 40031</t>
+          <t>14224; 38533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6898; 20728</t>
+          <t>6964; 21142</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3292; 16400</t>
+          <t>3051; 16212</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>986; 9645</t>
+          <t>980; 8731</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7722; 19512</t>
+          <t>8333; 20517</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19864; 42887</t>
+          <t>20748; 43088</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14022; 35615</t>
+          <t>14553; 36616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3206; 13914</t>
+          <t>3177; 15961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24317; 52723</t>
+          <t>24035; 51360</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>8667</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5513; 17997</t>
+          <t>4755; 18688</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7797; 23616</t>
+          <t>8520; 24271</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5079; 17172</t>
+          <t>4740; 17292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1933; 13764</t>
+          <t>1864; 12845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1927; 11657</t>
+          <t>1879; 10669</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5971; 21633</t>
+          <t>6175; 21048</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>859; 7215</t>
+          <t>854; 7315</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2154; 16990</t>
+          <t>1264; 6870</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8438; 24226</t>
+          <t>8607; 24563</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16803; 37581</t>
+          <t>17169; 38173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7398; 21544</t>
+          <t>7009; 20762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5263; 21701</t>
+          <t>4496; 15922</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>11366</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10281; 27129</t>
+          <t>10590; 27588</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3789; 16975</t>
+          <t>3086; 17149</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2619; 12054</t>
+          <t>2026; 12011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2493; 14257</t>
+          <t>2203; 13624</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2814; 13939</t>
+          <t>2779; 13078</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5157; 18580</t>
+          <t>5828; 19426</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6378</t>
+          <t>0; 6487</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1816; 8901</t>
+          <t>2485; 9918</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15258; 34724</t>
+          <t>15157; 34494</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11655; 29693</t>
+          <t>10910; 28354</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3606; 14019</t>
+          <t>3164; 15485</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5241; 19162</t>
+          <t>6362; 19978</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>11585</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10096; 27152</t>
+          <t>9452; 27182</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>920; 7929</t>
+          <t>913; 8009</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5705</t>
+          <t>0; 3844</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2658; 10043</t>
+          <t>3024; 11231</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9539; 25371</t>
+          <t>9787; 26227</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6855</t>
+          <t>0; 6607</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5380</t>
+          <t>0; 4447</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2741; 8930</t>
+          <t>2932; 9251</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23277; 46463</t>
+          <t>22287; 46856</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1932; 10972</t>
+          <t>1910; 11911</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6601</t>
+          <t>0; 6862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6556; 16262</t>
+          <t>7393; 17340</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>14208</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6924; 21083</t>
+          <t>7000; 20625</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6278; 22138</t>
+          <t>6367; 23170</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9339; 25813</t>
+          <t>8632; 25983</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4803; 18400</t>
+          <t>4580; 16791</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2940; 12986</t>
+          <t>3011; 13480</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1915; 10982</t>
+          <t>1954; 11523</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1846; 11202</t>
+          <t>1950; 12028</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2541; 10964</t>
+          <t>2114; 10680</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12442; 29827</t>
+          <t>12280; 29547</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9284; 29385</t>
+          <t>10126; 29317</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13342; 32398</t>
+          <t>13069; 33279</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9207; 26181</t>
+          <t>8721; 22196</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>23437</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6391; 18897</t>
+          <t>6246; 19477</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12878; 32217</t>
+          <t>12792; 34517</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6483; 23605</t>
+          <t>6528; 23620</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7995; 27630</t>
+          <t>8675; 27177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8484; 24900</t>
+          <t>9281; 23816</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8150; 27048</t>
+          <t>8395; 25609</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5939; 19652</t>
+          <t>6321; 20258</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2217; 12714</t>
+          <t>4184; 13879</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17855; 38404</t>
+          <t>17685; 37963</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25676; 51852</t>
+          <t>25419; 50908</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16159; 36422</t>
+          <t>16940; 38480</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11830; 36541</t>
+          <t>14803; 36645</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>28593</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12049; 30468</t>
+          <t>12293; 30645</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5124; 18264</t>
+          <t>4985; 17793</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17207; 37361</t>
+          <t>16144; 36423</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5359; 22049</t>
+          <t>8676; 23662</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36309; 64121</t>
+          <t>35840; 65862</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9217; 27512</t>
+          <t>9039; 27553</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8583; 26839</t>
+          <t>8870; 27051</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7189; 18996</t>
+          <t>8044; 20731</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54449; 86048</t>
+          <t>53765; 85085</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16475; 37831</t>
+          <t>16925; 38530</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28806; 55724</t>
+          <t>29335; 55711</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>14120; 35067</t>
+          <t>19640; 38859</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91149</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>62739</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>153888</t>
+          <t>157063</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>97585; 139614</t>
+          <t>96485; 139565</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>72908; 111940</t>
+          <t>70853; 113194</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>59381; 95608</t>
+          <t>61598; 97527</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67672; 116004</t>
+          <t>73559; 117256</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>92763; 135492</t>
+          <t>92490; 134696</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56535; 91782</t>
+          <t>57404; 91307</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34357; 63040</t>
+          <t>32986; 61015</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>47796; 77505</t>
+          <t>52833; 77940</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>201647; 263294</t>
+          <t>198013; 261137</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>139820; 193417</t>
+          <t>141231; 191928</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101890; 146255</t>
+          <t>103000; 146308</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>126820; 180417</t>
+          <t>135170; 182247</t>
         </is>
       </c>
     </row>
